--- a/AAII_Financials/Quarterly/MAGE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MAGE_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
   <si>
     <t>MAGE</t>
   </si>
@@ -656,136 +656,140 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -825,11 +829,11 @@
       <c r="O8" s="3">
         <v>0</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>0</v>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
@@ -844,19 +848,19 @@
         <v>0</v>
       </c>
       <c r="V8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>0</v>
       </c>
       <c r="AA8" s="3" t="s">
         <v>4</v>
@@ -873,8 +877,11 @@
       <c r="AE8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -920,11 +927,11 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R9" s="3">
-        <v>0</v>
+      <c r="R9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T9" s="3">
         <v>100</v>
@@ -933,17 +940,17 @@
         <v>100</v>
       </c>
       <c r="V9" s="3">
+        <v>100</v>
+      </c>
+      <c r="W9" s="3">
         <v>400</v>
       </c>
-      <c r="W9" s="3">
-        <v>100</v>
-      </c>
       <c r="X9" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y9" s="3">
         <v>300</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>4</v>
       </c>
@@ -962,8 +969,11 @@
       <c r="AE9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1009,11 +1019,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R10" s="3">
-        <v>0</v>
+      <c r="R10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S10" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T10" s="3">
         <v>-100</v>
@@ -1022,17 +1032,17 @@
         <v>-100</v>
       </c>
       <c r="V10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W10" s="3">
         <v>-300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>-200</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1051,8 +1061,11 @@
       <c r="AE10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1125,26 +1139,26 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>4</v>
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S12" s="3">
-        <v>0</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>4</v>
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T12" s="3">
+        <v>0</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V12" s="3">
-        <v>0</v>
+      <c r="V12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W12" s="3">
         <v>0</v>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1273,20 +1293,20 @@
       <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
         <v>1000</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1294,51 +1314,51 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>2100</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>3200</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W14" s="3">
         <v>400</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>300</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1351,8 +1371,11 @@
       <c r="AE14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1380,8 +1403,8 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>4</v>
+      <c r="L15" s="3">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>4</v>
@@ -1398,8 +1421,8 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="R15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1411,22 +1434,22 @@
         <v>0</v>
       </c>
       <c r="V15" s="3">
-        <v>100</v>
-      </c>
-      <c r="W15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X15" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>100</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>4</v>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,8 +1496,9 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1479,73 +1506,73 @@
         <v>100</v>
       </c>
       <c r="E17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
         <v>1100</v>
       </c>
-      <c r="G17" s="3">
-        <v>0</v>
-      </c>
       <c r="H17" s="3">
         <v>0</v>
       </c>
       <c r="I17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3">
         <v>100</v>
       </c>
       <c r="K17" s="3">
+        <v>100</v>
+      </c>
+      <c r="L17" s="3">
         <v>400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2200</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>200</v>
       </c>
       <c r="R17" s="3">
         <v>200</v>
       </c>
       <c r="S17" s="3">
+        <v>200</v>
+      </c>
+      <c r="T17" s="3">
         <v>3500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>800</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>200</v>
       </c>
       <c r="AB17" s="3">
         <v>200</v>
@@ -1557,10 +1584,13 @@
         <v>200</v>
       </c>
       <c r="AE17" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AF17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1568,71 +1598,71 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
         <v>-1100</v>
       </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
       <c r="H18" s="3">
         <v>0</v>
       </c>
       <c r="I18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3">
         <v>-100</v>
       </c>
       <c r="K18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L18" s="3">
         <v>-400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-400</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-200</v>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R18" s="3">
         <v>-200</v>
       </c>
       <c r="S18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="T18" s="3">
         <v>-3500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-300</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1648,8 +1678,11 @@
       <c r="AE18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1714,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1693,17 +1727,17 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
@@ -1722,11 +1756,11 @@
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -1741,19 +1775,19 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>300</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3" t="s">
-        <v>4</v>
+      <c r="Z20" s="3">
+        <v>0</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>4</v>
@@ -1770,8 +1804,11 @@
       <c r="AE20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1829,21 +1866,21 @@
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W21" s="3">
         <v>-1500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-200</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1859,8 +1896,11 @@
       <c r="AE21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1874,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H22" s="3">
         <v>100</v>
@@ -1883,10 +1923,10 @@
         <v>100</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L22" s="3">
         <v>100</v>
@@ -1898,40 +1938,40 @@
         <v>100</v>
       </c>
       <c r="O22" s="3">
+        <v>100</v>
+      </c>
+      <c r="P22" s="3">
         <v>200</v>
       </c>
-      <c r="P22" s="3">
-        <v>100</v>
-      </c>
       <c r="Q22" s="3">
         <v>100</v>
       </c>
       <c r="R22" s="3">
+        <v>100</v>
+      </c>
+      <c r="S22" s="3">
         <v>200</v>
       </c>
-      <c r="S22" s="3">
-        <v>100</v>
-      </c>
       <c r="T22" s="3">
+        <v>100</v>
+      </c>
+      <c r="U22" s="3">
         <v>200</v>
       </c>
-      <c r="U22" s="3">
-        <v>100</v>
-      </c>
       <c r="V22" s="3">
+        <v>100</v>
+      </c>
+      <c r="W22" s="3">
         <v>700</v>
       </c>
-      <c r="W22" s="3">
-        <v>100</v>
-      </c>
       <c r="X22" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y22" s="3">
         <v>400</v>
       </c>
-      <c r="Y22" s="3">
-        <v>100</v>
-      </c>
       <c r="Z22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
@@ -1948,97 +1988,103 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E23" s="3">
         <v>0</v>
       </c>
       <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
         <v>-900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-800</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-600</v>
       </c>
       <c r="O23" s="3">
         <v>-600</v>
       </c>
       <c r="P23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2126,8 +2172,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E26" s="3">
         <v>0</v>
       </c>
       <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
         <v>-900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-800</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-600</v>
       </c>
       <c r="O26" s="3">
         <v>-600</v>
       </c>
       <c r="P26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E27" s="3">
         <v>0</v>
       </c>
       <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
         <v>-900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2505,8 +2566,8 @@
       <c r="I29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="J29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -2530,22 +2591,22 @@
         <v>0</v>
       </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>-100</v>
-      </c>
-      <c r="S29" s="3">
-        <v>-200</v>
       </c>
       <c r="T29" s="3">
         <v>-200</v>
       </c>
       <c r="U29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V29" s="3">
         <v>-100</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2816,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2761,17 +2831,17 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
@@ -2790,11 +2860,11 @@
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -2809,19 +2879,19 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-300</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3" t="s">
-        <v>4</v>
+      <c r="Z32" s="3">
+        <v>0</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>4</v>
@@ -2838,97 +2908,103 @@
       <c r="AE32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E33" s="3">
         <v>0</v>
       </c>
       <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
         <v>-900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E35" s="3">
         <v>0</v>
       </c>
       <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
         <v>-900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,8 +3351,9 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3292,25 +3379,25 @@
         <v>0</v>
       </c>
       <c r="K41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L41" s="3">
+        <v>100</v>
+      </c>
+      <c r="M41" s="3">
         <v>200</v>
       </c>
-      <c r="M41" s="3">
-        <v>100</v>
-      </c>
       <c r="N41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O41" s="3">
         <v>0</v>
       </c>
       <c r="P41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R41" s="3">
         <v>0</v>
@@ -3334,10 +3421,10 @@
         <v>0</v>
       </c>
       <c r="Y41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA41" s="3">
         <v>0</v>
@@ -3354,8 +3441,11 @@
       <c r="AE41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3408,7 +3498,7 @@
         <v>0</v>
       </c>
       <c r="T42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U42" s="3">
         <v>100</v>
@@ -3428,8 +3518,8 @@
       <c r="Z42" s="3">
         <v>100</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>4</v>
+      <c r="AA42" s="3">
+        <v>100</v>
       </c>
       <c r="AB42" s="3" t="s">
         <v>4</v>
@@ -3443,8 +3533,11 @@
       <c r="AE42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3517,23 +3610,26 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>4</v>
+      <c r="AA43" s="3">
+        <v>0</v>
       </c>
       <c r="AB43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3621,8 +3717,11 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3630,10 +3729,10 @@
         <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G45" s="3">
         <v>0</v>
@@ -3669,10 +3768,10 @@
         <v>0</v>
       </c>
       <c r="R45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T45" s="3">
         <v>0</v>
@@ -3684,34 +3783,37 @@
         <v>0</v>
       </c>
       <c r="W45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X45" s="3">
         <v>100</v>
       </c>
       <c r="Y45" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z45" s="3">
         <v>200</v>
       </c>
-      <c r="Z45" s="3">
-        <v>100</v>
-      </c>
       <c r="AA45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB45" s="3">
         <v>200</v>
       </c>
       <c r="AC45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3719,10 +3821,10 @@
         <v>0</v>
       </c>
       <c r="E46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G46" s="3">
         <v>0</v>
@@ -3737,34 +3839,34 @@
         <v>0</v>
       </c>
       <c r="K46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L46" s="3">
+        <v>100</v>
+      </c>
+      <c r="M46" s="3">
         <v>200</v>
       </c>
-      <c r="M46" s="3">
-        <v>100</v>
-      </c>
       <c r="N46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O46" s="3">
         <v>0</v>
       </c>
       <c r="P46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U46" s="3">
         <v>100</v>
@@ -3776,31 +3878,34 @@
         <v>100</v>
       </c>
       <c r="X46" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y46" s="3">
         <v>200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>300</v>
-      </c>
-      <c r="AA46" s="3">
-        <v>200</v>
       </c>
       <c r="AB46" s="3">
         <v>200</v>
       </c>
       <c r="AC46" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3870,11 +3975,11 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA47" s="3">
-        <v>100</v>
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB47" s="3">
         <v>100</v>
@@ -3888,8 +3993,11 @@
       <c r="AE47" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3926,8 +4034,8 @@
       <c r="N48" s="3">
         <v>0</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
+      <c r="O48" s="3">
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>4</v>
@@ -3935,8 +4043,8 @@
       <c r="Q48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R48" s="3">
-        <v>1000</v>
+      <c r="R48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S48" s="3">
         <v>1000</v>
@@ -3948,7 +4056,7 @@
         <v>1000</v>
       </c>
       <c r="V48" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="W48" s="3">
         <v>1100</v>
@@ -3957,13 +4065,13 @@
         <v>1100</v>
       </c>
       <c r="Y48" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="Z48" s="3">
         <v>1200</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>4</v>
+      <c r="AA48" s="3">
+        <v>1200</v>
       </c>
       <c r="AB48" s="3" t="s">
         <v>4</v>
@@ -3977,8 +4085,11 @@
       <c r="AE48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3986,13 +4097,13 @@
         <v>1300</v>
       </c>
       <c r="E49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F49" s="3">
         <v>1200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>200</v>
-      </c>
-      <c r="G49" s="3">
-        <v>1200</v>
       </c>
       <c r="H49" s="3">
         <v>1200</v>
@@ -4007,7 +4118,7 @@
         <v>1200</v>
       </c>
       <c r="L49" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="M49" s="3">
         <v>1100</v>
@@ -4018,14 +4129,14 @@
       <c r="O49" s="3">
         <v>1100</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>4</v>
+      <c r="P49" s="3">
+        <v>1100</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R49" s="3">
-        <v>100</v>
+      <c r="R49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S49" s="3">
         <v>100</v>
@@ -4037,13 +4148,13 @@
         <v>100</v>
       </c>
       <c r="V49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W49" s="3">
+        <v>0</v>
+      </c>
+      <c r="X49" s="3">
         <v>400</v>
-      </c>
-      <c r="X49" s="3">
-        <v>300</v>
       </c>
       <c r="Y49" s="3">
         <v>300</v>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,8 +4361,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4288,11 +4408,11 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R52" s="3">
-        <v>400</v>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S52" s="3">
         <v>400</v>
@@ -4304,7 +4424,7 @@
         <v>400</v>
       </c>
       <c r="V52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="W52" s="3">
         <v>300</v>
@@ -4313,13 +4433,13 @@
         <v>300</v>
       </c>
       <c r="Y52" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Z52" s="3">
         <v>200</v>
       </c>
       <c r="AA52" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB52" s="3">
         <v>0</v>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,8 +4545,11 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4434,10 +4560,10 @@
         <v>1300</v>
       </c>
       <c r="F54" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G54" s="3">
         <v>200</v>
-      </c>
-      <c r="G54" s="3">
-        <v>1200</v>
       </c>
       <c r="H54" s="3">
         <v>1200</v>
@@ -4449,55 +4575,55 @@
         <v>1200</v>
       </c>
       <c r="K54" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="L54" s="3">
         <v>1300</v>
       </c>
       <c r="M54" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N54" s="3">
         <v>1200</v>
-      </c>
-      <c r="N54" s="3">
-        <v>1100</v>
       </c>
       <c r="O54" s="3">
         <v>1100</v>
       </c>
       <c r="P54" s="3">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="Q54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R54" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="S54" s="3">
         <v>1500</v>
       </c>
       <c r="T54" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="U54" s="3">
         <v>1600</v>
       </c>
       <c r="V54" s="3">
+        <v>1600</v>
+      </c>
+      <c r="W54" s="3">
         <v>1500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2000</v>
-      </c>
-      <c r="AA54" s="3">
-        <v>600</v>
       </c>
       <c r="AB54" s="3">
         <v>600</v>
@@ -4506,13 +4632,16 @@
         <v>600</v>
       </c>
       <c r="AD54" s="3">
+        <v>600</v>
+      </c>
+      <c r="AE54" s="3">
         <v>400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,8 +4707,9 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4592,10 +4723,10 @@
         <v>300</v>
       </c>
       <c r="G57" s="3">
+        <v>300</v>
+      </c>
+      <c r="H57" s="3">
         <v>200</v>
-      </c>
-      <c r="H57" s="3">
-        <v>300</v>
       </c>
       <c r="I57" s="3">
         <v>300</v>
@@ -4604,59 +4735,59 @@
         <v>300</v>
       </c>
       <c r="K57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L57" s="3">
         <v>200</v>
       </c>
       <c r="M57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N57" s="3">
         <v>300</v>
       </c>
       <c r="O57" s="3">
+        <v>300</v>
+      </c>
+      <c r="P57" s="3">
         <v>200</v>
       </c>
-      <c r="P57" s="3">
-        <v>100</v>
-      </c>
       <c r="Q57" s="3">
+        <v>100</v>
+      </c>
+      <c r="R57" s="3">
         <v>300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>600</v>
-      </c>
-      <c r="W57" s="3">
-        <v>500</v>
       </c>
       <c r="X57" s="3">
         <v>500</v>
       </c>
       <c r="Y57" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z57" s="3">
         <v>400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>200</v>
       </c>
-      <c r="AB57" s="3">
-        <v>100</v>
-      </c>
       <c r="AC57" s="3">
         <v>100</v>
       </c>
@@ -4666,8 +4797,11 @@
       <c r="AE57" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4675,10 +4809,10 @@
         <v>900</v>
       </c>
       <c r="E58" s="3">
+        <v>900</v>
+      </c>
+      <c r="F58" s="3">
         <v>800</v>
-      </c>
-      <c r="F58" s="3">
-        <v>900</v>
       </c>
       <c r="G58" s="3">
         <v>900</v>
@@ -4687,7 +4821,7 @@
         <v>900</v>
       </c>
       <c r="I58" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="J58" s="3">
         <v>800</v>
@@ -4696,31 +4830,31 @@
         <v>800</v>
       </c>
       <c r="L58" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="M58" s="3">
         <v>700</v>
       </c>
       <c r="N58" s="3">
+        <v>700</v>
+      </c>
+      <c r="O58" s="3">
         <v>500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1300</v>
-      </c>
-      <c r="T58" s="3">
-        <v>2700</v>
       </c>
       <c r="U58" s="3">
         <v>2700</v>
@@ -4729,7 +4863,7 @@
         <v>2700</v>
       </c>
       <c r="W58" s="3">
-        <v>2500</v>
+        <v>2700</v>
       </c>
       <c r="X58" s="3">
         <v>2500</v>
@@ -4741,27 +4875,30 @@
         <v>2500</v>
       </c>
       <c r="AA58" s="3">
-        <v>1300</v>
+        <v>2500</v>
       </c>
       <c r="AB58" s="3">
         <v>1300</v>
       </c>
       <c r="AC58" s="3">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="AD58" s="3">
         <v>1000</v>
       </c>
       <c r="AE58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AF58" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E59" s="3">
         <v>500</v>
@@ -4770,13 +4907,13 @@
         <v>500</v>
       </c>
       <c r="G59" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="H59" s="3">
         <v>700</v>
       </c>
       <c r="I59" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="J59" s="3">
         <v>400</v>
@@ -4788,153 +4925,159 @@
         <v>400</v>
       </c>
       <c r="M59" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="N59" s="3">
         <v>700</v>
       </c>
       <c r="O59" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="P59" s="3">
         <v>500</v>
       </c>
       <c r="Q59" s="3">
+        <v>500</v>
+      </c>
+      <c r="R59" s="3">
         <v>400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>600</v>
-      </c>
-      <c r="W59" s="3">
-        <v>500</v>
       </c>
       <c r="X59" s="3">
         <v>500</v>
       </c>
       <c r="Y59" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z59" s="3">
         <v>400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="E60" s="3">
         <v>1600</v>
       </c>
       <c r="F60" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G60" s="3">
         <v>1700</v>
-      </c>
-      <c r="G60" s="3">
-        <v>1900</v>
       </c>
       <c r="H60" s="3">
         <v>1900</v>
       </c>
       <c r="I60" s="3">
-        <v>1500</v>
+        <v>1900</v>
       </c>
       <c r="J60" s="3">
         <v>1500</v>
       </c>
       <c r="K60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L60" s="3">
         <v>1400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3900</v>
-      </c>
-      <c r="W60" s="3">
-        <v>3500</v>
       </c>
       <c r="X60" s="3">
         <v>3500</v>
       </c>
       <c r="Y60" s="3">
+        <v>3500</v>
+      </c>
+      <c r="Z60" s="3">
         <v>3300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1600</v>
-      </c>
-      <c r="AD60" s="3">
-        <v>1400</v>
       </c>
       <c r="AE60" s="3">
         <v>1400</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5022,8 +5165,11 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5070,7 +5216,7 @@
         <v>0</v>
       </c>
       <c r="R62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S62" s="3">
         <v>100</v>
@@ -5096,8 +5242,8 @@
       <c r="Z62" s="3">
         <v>100</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>4</v>
+      <c r="AA62" s="3">
+        <v>100</v>
       </c>
       <c r="AB62" s="3" t="s">
         <v>4</v>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5533,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="E66" s="3">
         <v>1600</v>
       </c>
       <c r="F66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G66" s="3">
         <v>1700</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1900</v>
       </c>
       <c r="H66" s="3">
         <v>1900</v>
       </c>
       <c r="I66" s="3">
-        <v>1500</v>
+        <v>1900</v>
       </c>
       <c r="J66" s="3">
         <v>1500</v>
       </c>
       <c r="K66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L66" s="3">
         <v>1400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1600</v>
-      </c>
-      <c r="AD66" s="3">
-        <v>1400</v>
       </c>
       <c r="AE66" s="3">
         <v>1400</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5711,7 +5879,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="N70" s="3">
         <v>1900</v>
@@ -5720,7 +5888,7 @@
         <v>1900</v>
       </c>
       <c r="P70" s="3">
-        <v>2400</v>
+        <v>1900</v>
       </c>
       <c r="Q70" s="3">
         <v>2400</v>
@@ -5732,7 +5900,7 @@
         <v>2400</v>
       </c>
       <c r="T70" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="U70" s="3">
         <v>0</v>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6027,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-19600</v>
+        <v>-19800</v>
       </c>
       <c r="E72" s="3">
         <v>-19600</v>
       </c>
       <c r="F72" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="G72" s="3">
         <v>-19500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-18600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-18500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-18100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-18000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-17800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-17300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-16700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-15800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-15200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-12200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-11900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-11300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-7600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-7000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-5400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-300</v>
+        <v>-500</v>
       </c>
       <c r="E76" s="3">
         <v>-300</v>
       </c>
       <c r="F76" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G76" s="3">
         <v>-1500</v>
-      </c>
-      <c r="G76" s="3">
-        <v>-700</v>
       </c>
       <c r="H76" s="3">
         <v>-700</v>
       </c>
       <c r="I76" s="3">
-        <v>-300</v>
+        <v>-700</v>
       </c>
       <c r="J76" s="3">
         <v>-300</v>
       </c>
       <c r="K76" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L76" s="3">
         <v>-100</v>
       </c>
-      <c r="L76" s="3">
-        <v>0</v>
-      </c>
       <c r="M76" s="3">
-        <v>-2300</v>
+        <v>0</v>
       </c>
       <c r="N76" s="3">
         <v>-2300</v>
       </c>
       <c r="O76" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="P76" s="3">
         <v>-2000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-3200</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>-3600</v>
       </c>
       <c r="R76" s="3">
         <v>-3600</v>
       </c>
       <c r="S76" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="T76" s="3">
         <v>-3400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-3100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-2700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-2500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-1700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AC76" s="3">
-        <v>-1000</v>
       </c>
       <c r="AD76" s="3">
         <v>-1000</v>
       </c>
       <c r="AE76" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AF76" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E81" s="3">
         <v>0</v>
       </c>
       <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
         <v>-900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6644,8 +6843,8 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>4</v>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>4</v>
@@ -6653,23 +6852,23 @@
       <c r="Q83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="R83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
       <c r="T83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
@@ -6677,8 +6876,8 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>4</v>
+      <c r="Z83" s="3">
+        <v>0</v>
       </c>
       <c r="AA83" s="3" t="s">
         <v>4</v>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,20 +7354,23 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E89" s="3">
+        <v>100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
       <c r="G89" s="3">
         <v>0</v>
       </c>
@@ -7161,7 +7378,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J89" s="3">
         <v>-100</v>
@@ -7176,10 +7393,10 @@
         <v>-100</v>
       </c>
       <c r="N89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P89" s="3">
         <v>-100</v>
@@ -7188,34 +7405,34 @@
         <v>-100</v>
       </c>
       <c r="R89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
         <v>-200</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-100</v>
       </c>
       <c r="U89" s="3">
         <v>-100</v>
       </c>
       <c r="V89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W89" s="3">
         <v>-600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>-100</v>
       </c>
       <c r="AB89" s="3">
         <v>-100</v>
@@ -7229,8 +7446,11 @@
       <c r="AE89" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,17 +7482,18 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
@@ -7295,11 +7516,11 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -7318,14 +7539,14 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>4</v>
@@ -7333,8 +7554,8 @@
       <c r="Y91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
@@ -7351,8 +7572,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,17 +7756,20 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
@@ -7558,20 +7788,20 @@
       <c r="K94" s="3">
         <v>0</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N94" s="3">
-        <v>-100</v>
+      <c r="N94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O94" s="3">
         <v>-100</v>
       </c>
       <c r="P94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
@@ -7583,7 +7813,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U94" s="3">
         <v>-100</v>
@@ -7595,31 +7825,34 @@
         <v>-100</v>
       </c>
       <c r="X94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-900</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
       <c r="AB94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC94" s="3">
         <v>-100</v>
       </c>
       <c r="AD94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,8 +8250,11 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8016,10 +8262,10 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G100" s="3">
         <v>0</v>
@@ -8037,67 +8283,70 @@
         <v>0</v>
       </c>
       <c r="L100" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M100" s="3">
         <v>200</v>
       </c>
       <c r="N100" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P100" s="3">
         <v>100</v>
       </c>
       <c r="Q100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
       <c r="S100" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="T100" s="3">
         <v>200</v>
       </c>
       <c r="U100" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V100" s="3">
+        <v>100</v>
+      </c>
+      <c r="W100" s="3">
         <v>700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>200</v>
       </c>
-      <c r="X100" s="3">
-        <v>100</v>
-      </c>
       <c r="Y100" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z100" s="3">
         <v>200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1000</v>
       </c>
-      <c r="AA100" s="3">
-        <v>100</v>
-      </c>
       <c r="AB100" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC100" s="3">
         <v>200</v>
       </c>
       <c r="AD100" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8141,13 +8390,13 @@
         <v>0</v>
       </c>
       <c r="Q101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R101" s="3">
         <v>100</v>
       </c>
       <c r="S101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -8179,14 +8428,17 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>4</v>
+      <c r="AD101" s="3">
+        <v>0</v>
       </c>
       <c r="AE101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8209,28 +8461,28 @@
         <v>0</v>
       </c>
       <c r="J102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K102" s="3">
         <v>-100</v>
       </c>
       <c r="L102" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="M102" s="3">
         <v>100</v>
       </c>
       <c r="N102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O102" s="3">
         <v>0</v>
       </c>
       <c r="P102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R102" s="3">
         <v>0</v>
@@ -8251,13 +8503,13 @@
         <v>0</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-100</v>
       </c>
-      <c r="Y102" s="3">
-        <v>100</v>
-      </c>
       <c r="Z102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA102" s="3">
         <v>0</v>
@@ -8272,6 +8524,9 @@
         <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MAGE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MAGE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
   <si>
     <t>MAGE</t>
   </si>
@@ -656,140 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -832,14 +839,14 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>4</v>
+      <c r="Q8" s="3">
+        <v>0</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -851,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="W8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X8" s="3">
         <v>0</v>
@@ -862,11 +869,11 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB8" s="3" t="s">
-        <v>4</v>
+      <c r="AA8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>0</v>
       </c>
       <c r="AC8" s="3" t="s">
         <v>4</v>
@@ -880,8 +887,14 @@
       <c r="AF8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -930,33 +943,33 @@
       <c r="R9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S9" s="3">
-        <v>0</v>
-      </c>
-      <c r="T9" s="3">
-        <v>100</v>
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V9" s="3">
         <v>100</v>
       </c>
       <c r="W9" s="3">
+        <v>100</v>
+      </c>
+      <c r="X9" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y9" s="3">
         <v>400</v>
       </c>
-      <c r="X9" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA9" s="3">
         <v>300</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB9" s="3" t="s">
         <v>4</v>
       </c>
@@ -972,8 +985,14 @@
       <c r="AF9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1022,33 +1041,33 @@
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S10" s="3">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3">
-        <v>-100</v>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U10" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V10" s="3">
         <v>-100</v>
       </c>
       <c r="W10" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="X10" s="3">
         <v>-100</v>
       </c>
       <c r="Y10" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA10" s="3">
         <v>-200</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1064,8 +1083,14 @@
       <c r="AF10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1123,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1142,29 +1169,29 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q12" s="3">
-        <v>0</v>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T12" s="3">
-        <v>0</v>
+      <c r="S12" s="3">
+        <v>0</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W12" s="3">
-        <v>0</v>
-      </c>
-      <c r="X12" s="3">
-        <v>0</v>
+      <c r="V12" s="3">
+        <v>0</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y12" s="3">
         <v>0</v>
@@ -1190,8 +1217,14 @@
       <c r="AF12" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,89 +1315,95 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
+      <c r="E14" s="3">
+        <v>1200</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
         <v>1000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>2100</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>3200</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="3">
         <v>400</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>100</v>
-      </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
       <c r="AA14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>300</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1374,8 +1413,14 @@
       <c r="AF14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1406,11 +1451,11 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>4</v>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>4</v>
@@ -1424,11 +1469,11 @@
       <c r="R15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
-      </c>
-      <c r="T15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
@@ -1437,25 +1482,25 @@
         <v>0</v>
       </c>
       <c r="W15" s="3">
-        <v>100</v>
-      </c>
-      <c r="X15" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
       </c>
       <c r="Y15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>100</v>
+        <v>100</v>
+      </c>
+      <c r="Z15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC15" s="3" t="s">
-        <v>4</v>
+      <c r="AB15" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>0</v>
       </c>
       <c r="AD15" s="3" t="s">
         <v>4</v>
@@ -1466,8 +1511,14 @@
       <c r="AF15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,8 +1548,10 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1506,79 +1559,79 @@
         <v>100</v>
       </c>
       <c r="E17" s="3">
-        <v>100</v>
+        <v>1300</v>
       </c>
       <c r="F17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G17" s="3">
+        <v>100</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
         <v>1100</v>
       </c>
-      <c r="H17" s="3">
-        <v>0</v>
-      </c>
-      <c r="I17" s="3">
-        <v>0</v>
-      </c>
       <c r="J17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L17" s="3">
+        <v>100</v>
+      </c>
+      <c r="M17" s="3">
+        <v>100</v>
+      </c>
+      <c r="N17" s="3">
         <v>400</v>
-      </c>
-      <c r="M17" s="3">
-        <v>500</v>
-      </c>
-      <c r="N17" s="3">
-        <v>700</v>
       </c>
       <c r="O17" s="3">
         <v>500</v>
       </c>
       <c r="P17" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>500</v>
+      </c>
+      <c r="R17" s="3">
         <v>400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>3500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>800</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>200</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>200</v>
       </c>
       <c r="AD17" s="3">
         <v>200</v>
@@ -1587,10 +1640,16 @@
         <v>200</v>
       </c>
       <c r="AF17" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AG17" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1598,77 +1657,77 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-100</v>
       </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
       <c r="G18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
         <v>-1100</v>
       </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
       <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
         <v>-100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-400</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-500</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-700</v>
       </c>
       <c r="O18" s="3">
         <v>-500</v>
       </c>
       <c r="P18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R18" s="3">
         <v>-400</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T18" s="3">
         <v>-200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-3500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-1800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-300</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1681,8 +1740,14 @@
       <c r="AF18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1780,10 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1724,26 +1791,26 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1759,14 +1826,14 @@
       <c r="P20" s="3">
         <v>0</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>4</v>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
@@ -1778,22 +1845,22 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>300</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB20" s="3" t="s">
-        <v>4</v>
+      <c r="AB20" s="3">
+        <v>0</v>
       </c>
       <c r="AC20" s="3" t="s">
         <v>4</v>
@@ -1807,8 +1874,14 @@
       <c r="AF20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1869,24 +1942,24 @@
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-1500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-200</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1899,8 +1972,14 @@
       <c r="AF21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1917,22 +1996,22 @@
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22" s="3">
         <v>100</v>
       </c>
       <c r="M22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N22" s="3">
         <v>100</v>
@@ -1941,16 +2020,16 @@
         <v>100</v>
       </c>
       <c r="P22" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>100</v>
+      </c>
+      <c r="R22" s="3">
         <v>200</v>
       </c>
-      <c r="Q22" s="3">
-        <v>100</v>
-      </c>
-      <c r="R22" s="3">
-        <v>100</v>
-      </c>
       <c r="S22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T22" s="3">
         <v>100</v>
@@ -1962,22 +2041,22 @@
         <v>100</v>
       </c>
       <c r="W22" s="3">
+        <v>200</v>
+      </c>
+      <c r="X22" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y22" s="3">
         <v>700</v>
       </c>
-      <c r="X22" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA22" s="3">
         <v>400</v>
       </c>
-      <c r="Z22" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>0</v>
-      </c>
       <c r="AB22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -1991,100 +2070,112 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-200</v>
       </c>
-      <c r="E23" s="3">
-        <v>0</v>
-      </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
       <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
         <v>-900</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-400</v>
       </c>
       <c r="J23" s="3">
         <v>-100</v>
       </c>
       <c r="K23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M23" s="3">
         <v>-200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-500</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-600</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-800</v>
       </c>
       <c r="O23" s="3">
         <v>-600</v>
       </c>
       <c r="P23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="S23" s="3">
         <v>-2200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-3600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-2300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-300</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-900</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>-200</v>
       </c>
       <c r="AC23" s="3">
         <v>-900</v>
       </c>
       <c r="AD23" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AE23" s="3">
-        <v>-200</v>
+        <v>-900</v>
       </c>
       <c r="AF23" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2175,8 +2266,14 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2364,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-200</v>
       </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
       <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
         <v>-900</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-400</v>
       </c>
       <c r="J26" s="3">
         <v>-100</v>
       </c>
       <c r="K26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M26" s="3">
         <v>-200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-500</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-600</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-800</v>
       </c>
       <c r="O26" s="3">
         <v>-600</v>
       </c>
       <c r="P26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="S26" s="3">
         <v>-2200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-3600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-2300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-300</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-900</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>-200</v>
       </c>
       <c r="AC26" s="3">
         <v>-900</v>
       </c>
       <c r="AD26" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AE26" s="3">
-        <v>-200</v>
+        <v>-900</v>
       </c>
       <c r="AF26" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AH26" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-200</v>
       </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
       <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
         <v>-900</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-400</v>
       </c>
       <c r="J27" s="3">
         <v>-100</v>
       </c>
       <c r="K27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M27" s="3">
         <v>-200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-500</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-700</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-800</v>
       </c>
       <c r="O27" s="3">
         <v>-700</v>
       </c>
       <c r="P27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="R27" s="3">
         <v>-600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-2300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-3600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-2600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-300</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>-900</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>-200</v>
       </c>
       <c r="AC27" s="3">
         <v>-900</v>
       </c>
       <c r="AD27" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AE27" s="3">
-        <v>-200</v>
+        <v>-900</v>
       </c>
       <c r="AF27" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AH27" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,37 +2658,43 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2594,25 +2715,25 @@
         <v>0</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>-100</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>-200</v>
       </c>
-      <c r="U29" s="3">
+      <c r="W29" s="3">
         <v>-200</v>
       </c>
-      <c r="V29" s="3">
+      <c r="X29" s="3">
         <v>-100</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z29" s="3">
         <v>0</v>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2952,14 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2828,26 +2967,26 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -2863,14 +3002,14 @@
       <c r="P32" s="3">
         <v>0</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>4</v>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T32" s="3">
         <v>0</v>
@@ -2882,22 +3021,22 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-300</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB32" s="3" t="s">
-        <v>4</v>
+      <c r="AB32" s="3">
+        <v>0</v>
       </c>
       <c r="AC32" s="3" t="s">
         <v>4</v>
@@ -2911,100 +3050,112 @@
       <c r="AF32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-200</v>
       </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
       <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
         <v>-900</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-400</v>
       </c>
       <c r="J33" s="3">
         <v>-100</v>
       </c>
       <c r="K33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M33" s="3">
         <v>-200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-500</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-700</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-800</v>
       </c>
       <c r="O33" s="3">
         <v>-700</v>
       </c>
       <c r="P33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="R33" s="3">
         <v>-600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-2300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-3700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-2600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-300</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>-900</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>-200</v>
       </c>
       <c r="AC33" s="3">
         <v>-900</v>
       </c>
       <c r="AD33" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AE33" s="3">
-        <v>-200</v>
+        <v>-900</v>
       </c>
       <c r="AF33" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AH33" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3246,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-200</v>
       </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
       <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
         <v>-900</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-400</v>
       </c>
       <c r="J35" s="3">
         <v>-100</v>
       </c>
       <c r="K35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M35" s="3">
         <v>-200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-500</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-700</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-800</v>
       </c>
       <c r="O35" s="3">
         <v>-700</v>
       </c>
       <c r="P35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="R35" s="3">
         <v>-600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-2300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-3700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-2600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-300</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>-900</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>-200</v>
       </c>
       <c r="AC35" s="3">
         <v>-900</v>
       </c>
       <c r="AD35" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AE35" s="3">
-        <v>-200</v>
+        <v>-900</v>
       </c>
       <c r="AF35" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AH35" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,8 +3523,10 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3382,28 +3555,28 @@
         <v>0</v>
       </c>
       <c r="L41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M41" s="3">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3">
+        <v>100</v>
+      </c>
+      <c r="O41" s="3">
         <v>200</v>
       </c>
-      <c r="N41" s="3">
-        <v>100</v>
-      </c>
-      <c r="O41" s="3">
-        <v>0</v>
-      </c>
       <c r="P41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R41" s="3">
         <v>0</v>
       </c>
       <c r="S41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T41" s="3">
         <v>0</v>
@@ -3424,13 +3597,13 @@
         <v>0</v>
       </c>
       <c r="Z41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA41" s="3">
         <v>0</v>
       </c>
       <c r="AB41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC41" s="3">
         <v>0</v>
@@ -3444,8 +3617,14 @@
       <c r="AF41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3501,10 +3680,10 @@
         <v>0</v>
       </c>
       <c r="U42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W42" s="3">
         <v>100</v>
@@ -3521,11 +3700,11 @@
       <c r="AA42" s="3">
         <v>100</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC42" s="3" t="s">
-        <v>4</v>
+      <c r="AB42" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>100</v>
       </c>
       <c r="AD42" s="3" t="s">
         <v>4</v>
@@ -3536,8 +3715,14 @@
       <c r="AF42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3613,14 +3798,14 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>0</v>
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE43" s="3" t="s">
         <v>4</v>
@@ -3628,8 +3813,14 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,25 +3911,31 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G45" s="3">
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I45" s="3">
         <v>0</v>
@@ -3771,13 +3968,13 @@
         <v>0</v>
       </c>
       <c r="S45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T45" s="3">
         <v>0</v>
       </c>
       <c r="U45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V45" s="3">
         <v>0</v>
@@ -3786,13 +3983,13 @@
         <v>0</v>
       </c>
       <c r="X45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA45" s="3">
         <v>100</v>
@@ -3801,19 +3998,25 @@
         <v>200</v>
       </c>
       <c r="AC45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD45" s="3">
         <v>200</v>
       </c>
-      <c r="AD45" s="3">
-        <v>100</v>
-      </c>
       <c r="AE45" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AF45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3824,13 +4027,13 @@
         <v>0</v>
       </c>
       <c r="F46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G46" s="3">
         <v>0</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I46" s="3">
         <v>0</v>
@@ -3842,22 +4045,22 @@
         <v>0</v>
       </c>
       <c r="L46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M46" s="3">
+        <v>0</v>
+      </c>
+      <c r="N46" s="3">
+        <v>100</v>
+      </c>
+      <c r="O46" s="3">
         <v>200</v>
       </c>
-      <c r="N46" s="3">
-        <v>100</v>
-      </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R46" s="3">
         <v>0</v>
@@ -3872,7 +4075,7 @@
         <v>100</v>
       </c>
       <c r="V46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W46" s="3">
         <v>100</v>
@@ -3881,31 +4084,37 @@
         <v>100</v>
       </c>
       <c r="Y46" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z46" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA46" s="3">
         <v>200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>200</v>
       </c>
-      <c r="AD46" s="3">
-        <v>100</v>
-      </c>
-      <c r="AE46" s="3">
-        <v>0</v>
-      </c>
       <c r="AF46" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3978,14 +4187,14 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>4</v>
+      <c r="AA47" s="3">
+        <v>0</v>
       </c>
       <c r="AB47" s="3">
-        <v>100</v>
-      </c>
-      <c r="AC47" s="3">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD47" s="3">
         <v>100</v>
@@ -3996,8 +4205,14 @@
       <c r="AF47" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4037,20 +4252,20 @@
       <c r="O48" s="3">
         <v>0</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S48" s="3">
-        <v>1000</v>
-      </c>
-      <c r="T48" s="3">
-        <v>1000</v>
+      <c r="S48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U48" s="3">
         <v>1000</v>
@@ -4059,26 +4274,26 @@
         <v>1000</v>
       </c>
       <c r="W48" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="X48" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="Y48" s="3">
         <v>1100</v>
       </c>
       <c r="Z48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AA48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB48" s="3">
         <v>1200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>1200</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>4</v>
       </c>
@@ -4088,28 +4303,34 @@
       <c r="AF48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>500</v>
+      </c>
+      <c r="E49" s="3">
+        <v>100</v>
+      </c>
+      <c r="F49" s="3">
         <v>1300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1300</v>
-      </c>
-      <c r="F49" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G49" s="3">
-        <v>200</v>
       </c>
       <c r="H49" s="3">
         <v>1200</v>
       </c>
       <c r="I49" s="3">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="J49" s="3">
         <v>1200</v>
@@ -4121,10 +4342,10 @@
         <v>1200</v>
       </c>
       <c r="M49" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="N49" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="O49" s="3">
         <v>1100</v>
@@ -4132,17 +4353,17 @@
       <c r="P49" s="3">
         <v>1100</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S49" s="3">
-        <v>100</v>
-      </c>
-      <c r="T49" s="3">
-        <v>100</v>
+      <c r="Q49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="R49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U49" s="3">
         <v>100</v>
@@ -4151,16 +4372,16 @@
         <v>100</v>
       </c>
       <c r="W49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X49" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="3">
         <v>400</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>300</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>300</v>
       </c>
       <c r="AA49" s="3">
         <v>300</v>
@@ -4180,8 +4401,14 @@
       <c r="AF49" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4597,14 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4411,14 +4650,14 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>4</v>
+      <c r="R52" s="3">
+        <v>0</v>
       </c>
       <c r="S52" s="3">
-        <v>400</v>
-      </c>
-      <c r="T52" s="3">
-        <v>400</v>
+        <v>0</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U52" s="3">
         <v>400</v>
@@ -4427,26 +4666,26 @@
         <v>400</v>
       </c>
       <c r="W52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="X52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Y52" s="3">
         <v>300</v>
       </c>
       <c r="Z52" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA52" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB52" s="3">
         <v>200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>200</v>
       </c>
-      <c r="AB52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>0</v>
-      </c>
       <c r="AD52" s="3">
         <v>0</v>
       </c>
@@ -4456,8 +4695,14 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,28 +4793,34 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1300</v>
+        <v>500</v>
       </c>
       <c r="E54" s="3">
-        <v>1300</v>
+        <v>100</v>
       </c>
       <c r="F54" s="3">
         <v>1300</v>
       </c>
       <c r="G54" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H54" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I54" s="3">
         <v>200</v>
-      </c>
-      <c r="H54" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I54" s="3">
-        <v>1200</v>
       </c>
       <c r="J54" s="3">
         <v>1200</v>
@@ -4578,70 +4829,76 @@
         <v>1200</v>
       </c>
       <c r="L54" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M54" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N54" s="3">
         <v>1300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1100</v>
       </c>
-      <c r="Q54" s="3">
-        <v>100</v>
-      </c>
-      <c r="R54" s="3">
-        <v>0</v>
-      </c>
       <c r="S54" s="3">
+        <v>100</v>
+      </c>
+      <c r="T54" s="3">
+        <v>0</v>
+      </c>
+      <c r="U54" s="3">
         <v>1500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>2000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>2200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>2000</v>
-      </c>
-      <c r="AB54" s="3">
-        <v>600</v>
-      </c>
-      <c r="AC54" s="3">
-        <v>600</v>
       </c>
       <c r="AD54" s="3">
         <v>600</v>
       </c>
       <c r="AE54" s="3">
+        <v>600</v>
+      </c>
+      <c r="AF54" s="3">
+        <v>600</v>
+      </c>
+      <c r="AG54" s="3">
         <v>400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,16 +4967,18 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E57" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F57" s="3">
         <v>300</v>
@@ -4726,82 +4987,88 @@
         <v>300</v>
       </c>
       <c r="H57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I57" s="3">
         <v>300</v>
       </c>
       <c r="J57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K57" s="3">
         <v>300</v>
       </c>
       <c r="L57" s="3">
+        <v>300</v>
+      </c>
+      <c r="M57" s="3">
+        <v>300</v>
+      </c>
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>200</v>
       </c>
-      <c r="Q57" s="3">
-        <v>100</v>
-      </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
+        <v>100</v>
+      </c>
+      <c r="T57" s="3">
         <v>300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>600</v>
-      </c>
-      <c r="T57" s="3">
-        <v>700</v>
-      </c>
-      <c r="U57" s="3">
-        <v>900</v>
       </c>
       <c r="V57" s="3">
         <v>700</v>
       </c>
       <c r="W57" s="3">
+        <v>900</v>
+      </c>
+      <c r="X57" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y57" s="3">
         <v>600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>200</v>
       </c>
-      <c r="AC57" s="3">
-        <v>100</v>
-      </c>
-      <c r="AD57" s="3">
-        <v>100</v>
-      </c>
       <c r="AE57" s="3">
         <v>100</v>
       </c>
       <c r="AF57" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4812,64 +5079,64 @@
         <v>900</v>
       </c>
       <c r="F58" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="G58" s="3">
         <v>900</v>
       </c>
       <c r="H58" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="I58" s="3">
         <v>900</v>
       </c>
       <c r="J58" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="K58" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="L58" s="3">
         <v>800</v>
       </c>
       <c r="M58" s="3">
+        <v>800</v>
+      </c>
+      <c r="N58" s="3">
+        <v>800</v>
+      </c>
+      <c r="O58" s="3">
         <v>700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>500</v>
-      </c>
-      <c r="P58" s="3">
-        <v>400</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>300</v>
       </c>
       <c r="R58" s="3">
         <v>400</v>
       </c>
       <c r="S58" s="3">
+        <v>300</v>
+      </c>
+      <c r="T58" s="3">
+        <v>400</v>
+      </c>
+      <c r="U58" s="3">
         <v>1400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1300</v>
-      </c>
-      <c r="U58" s="3">
-        <v>2700</v>
-      </c>
-      <c r="V58" s="3">
-        <v>2700</v>
       </c>
       <c r="W58" s="3">
         <v>2700</v>
       </c>
       <c r="X58" s="3">
-        <v>2500</v>
+        <v>2700</v>
       </c>
       <c r="Y58" s="3">
-        <v>2500</v>
+        <v>2700</v>
       </c>
       <c r="Z58" s="3">
         <v>2500</v>
@@ -4878,22 +5145,28 @@
         <v>2500</v>
       </c>
       <c r="AB58" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AC58" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AD58" s="3">
         <v>1300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>1300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>1000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>1000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4904,22 +5177,22 @@
         <v>500</v>
       </c>
       <c r="F59" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G59" s="3">
         <v>500</v>
       </c>
       <c r="H59" s="3">
+        <v>500</v>
+      </c>
+      <c r="I59" s="3">
+        <v>500</v>
+      </c>
+      <c r="J59" s="3">
         <v>700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>700</v>
-      </c>
-      <c r="J59" s="3">
-        <v>400</v>
-      </c>
-      <c r="K59" s="3">
-        <v>400</v>
       </c>
       <c r="L59" s="3">
         <v>400</v>
@@ -4928,19 +5201,19 @@
         <v>400</v>
       </c>
       <c r="N59" s="3">
+        <v>400</v>
+      </c>
+      <c r="O59" s="3">
+        <v>400</v>
+      </c>
+      <c r="P59" s="3">
         <v>700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>500</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>500</v>
-      </c>
-      <c r="R59" s="3">
-        <v>400</v>
       </c>
       <c r="S59" s="3">
         <v>500</v>
@@ -4949,135 +5222,147 @@
         <v>400</v>
       </c>
       <c r="U59" s="3">
+        <v>500</v>
+      </c>
+      <c r="V59" s="3">
+        <v>400</v>
+      </c>
+      <c r="W59" s="3">
         <v>1000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>500</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>400</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>300</v>
       </c>
       <c r="AB59" s="3">
         <v>400</v>
       </c>
       <c r="AC59" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD59" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE59" s="3">
         <v>700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E60" s="3">
         <v>1800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G60" s="3">
         <v>1600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1500</v>
-      </c>
-      <c r="P60" s="3">
-        <v>1100</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>900</v>
       </c>
       <c r="R60" s="3">
         <v>1100</v>
       </c>
       <c r="S60" s="3">
+        <v>900</v>
+      </c>
+      <c r="T60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U60" s="3">
         <v>2600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>2400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>4600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>4200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>3900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>3500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>3500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>3300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>3100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>1900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>2100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>1600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>1400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5168,8 +5453,14 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5219,10 +5510,10 @@
         <v>0</v>
       </c>
       <c r="S62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U62" s="3">
         <v>100</v>
@@ -5245,11 +5536,11 @@
       <c r="AA62" s="3">
         <v>100</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC62" s="3" t="s">
-        <v>4</v>
+      <c r="AB62" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC62" s="3">
+        <v>100</v>
       </c>
       <c r="AD62" s="3" t="s">
         <v>4</v>
@@ -5260,8 +5551,14 @@
       <c r="AF62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5845,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G66" s="3">
         <v>1600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1500</v>
-      </c>
-      <c r="P66" s="3">
-        <v>1100</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>900</v>
       </c>
       <c r="R66" s="3">
         <v>1100</v>
       </c>
       <c r="S66" s="3">
+        <v>900</v>
+      </c>
+      <c r="T66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U66" s="3">
         <v>2700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>2500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>4700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>4300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>4000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>3700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>3600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>3400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>3200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>2100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>1600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>1400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5882,19 +6217,19 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="O70" s="3">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="P70" s="3">
         <v>1900</v>
       </c>
       <c r="Q70" s="3">
-        <v>2400</v>
+        <v>1900</v>
       </c>
       <c r="R70" s="3">
-        <v>2400</v>
+        <v>1900</v>
       </c>
       <c r="S70" s="3">
         <v>2400</v>
@@ -5903,10 +6238,10 @@
         <v>2400</v>
       </c>
       <c r="U70" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="V70" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="W70" s="3">
         <v>0</v>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-19800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-19600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-19600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-19500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-18600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-18500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-18100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-18000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-17800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-17300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-16700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-15800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-14500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-12200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-11900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-11300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-7600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-7000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-6700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F76" s="3">
         <v>-500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-1500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-100</v>
       </c>
-      <c r="M76" s="3">
-        <v>0</v>
-      </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
+        <v>0</v>
+      </c>
+      <c r="P76" s="3">
         <v>-2300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-2300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-3200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-3600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-3600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-3400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>-3100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>-2700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>-2500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>-1800</v>
-      </c>
-      <c r="Z76" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="AA76" s="3">
-        <v>-1200</v>
       </c>
       <c r="AB76" s="3">
         <v>-1300</v>
       </c>
       <c r="AC76" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AD76" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AE76" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6959,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-200</v>
       </c>
-      <c r="E81" s="3">
-        <v>0</v>
-      </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
       <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
         <v>-900</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-400</v>
       </c>
       <c r="J81" s="3">
         <v>-100</v>
       </c>
       <c r="K81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M81" s="3">
         <v>-200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-500</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-700</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-800</v>
       </c>
       <c r="O81" s="3">
         <v>-700</v>
       </c>
       <c r="P81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="R81" s="3">
         <v>-600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-2300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-3700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-2600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-300</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>-900</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>-200</v>
       </c>
       <c r="AC81" s="3">
         <v>-900</v>
       </c>
       <c r="AD81" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AE81" s="3">
-        <v>-200</v>
+        <v>-900</v>
       </c>
       <c r="AF81" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AH81" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7200,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6846,23 +7243,23 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>4</v>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -6874,16 +7271,16 @@
         <v>0</v>
       </c>
       <c r="Y83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB83" s="3" t="s">
-        <v>4</v>
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>0</v>
       </c>
       <c r="AC83" s="3" t="s">
         <v>4</v>
@@ -6897,8 +7294,14 @@
       <c r="AF83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,34 +7784,40 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
+        <v>100</v>
+      </c>
+      <c r="H89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
       <c r="I89" s="3">
         <v>0</v>
       </c>
       <c r="J89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L89" s="3">
         <v>-100</v>
@@ -7396,37 +7829,37 @@
         <v>-100</v>
       </c>
       <c r="O89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P89" s="3">
         <v>-100</v>
       </c>
       <c r="Q89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R89" s="3">
         <v>-100</v>
       </c>
       <c r="S89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
         <v>-200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-100</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="W89" s="3">
-        <v>-600</v>
       </c>
       <c r="X89" s="3">
         <v>-100</v>
       </c>
       <c r="Y89" s="3">
-        <v>-200</v>
+        <v>-600</v>
       </c>
       <c r="Z89" s="3">
         <v>-100</v>
@@ -7438,7 +7871,7 @@
         <v>-100</v>
       </c>
       <c r="AC89" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AD89" s="3">
         <v>-100</v>
@@ -7449,8 +7882,14 @@
       <c r="AF89" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH89" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7922,10 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7492,11 +7933,11 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
@@ -7519,14 +7960,14 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
@@ -7542,8 +7983,8 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -7551,17 +7992,17 @@
       <c r="X91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>4</v>
+      <c r="Y91" s="3">
+        <v>0</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
@@ -7575,8 +8016,14 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,23 +8212,29 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
@@ -7791,24 +8250,24 @@
       <c r="L94" s="3">
         <v>0</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
@@ -7816,10 +8275,10 @@
         <v>0</v>
       </c>
       <c r="U94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W94" s="3">
         <v>-100</v>
@@ -7828,31 +8287,37 @@
         <v>-100</v>
       </c>
       <c r="Y94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-900</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-100</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>0</v>
       </c>
       <c r="AF94" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,25 +8738,31 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
       </c>
       <c r="F100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I100" s="3">
         <v>0</v>
@@ -8286,67 +8777,73 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>100</v>
-      </c>
       <c r="Q100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>200</v>
       </c>
-      <c r="V100" s="3">
-        <v>100</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y100" s="3">
         <v>700</v>
-      </c>
-      <c r="X100" s="3">
-        <v>200</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>100</v>
       </c>
       <c r="Z100" s="3">
         <v>200</v>
       </c>
       <c r="AA100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB100" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC100" s="3">
         <v>1000</v>
       </c>
-      <c r="AB100" s="3">
-        <v>100</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE100" s="3">
         <v>200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>200</v>
       </c>
-      <c r="AE100" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8393,16 +8890,16 @@
         <v>0</v>
       </c>
       <c r="R101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
@@ -8431,14 +8928,20 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF101" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8464,31 +8967,31 @@
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="M102" s="3">
-        <v>100</v>
-      </c>
-      <c r="N102" s="3">
-        <v>100</v>
-      </c>
       <c r="O102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R102" s="3">
         <v>0</v>
       </c>
       <c r="S102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T102" s="3">
         <v>0</v>
@@ -8506,16 +9009,16 @@
         <v>0</v>
       </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-100</v>
       </c>
-      <c r="Z102" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
       <c r="AB102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC102" s="3">
         <v>0</v>
@@ -8527,6 +9030,12 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-100</v>
       </c>
     </row>
